--- a/UPSC_MV-08_BM-02_Danh_muc_ky_quy.xlsx
+++ b/UPSC_MV-08_BM-02_Danh_muc_ky_quy.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Danh mục ký quỹ" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="BM-02.1 Day du" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="BM-02.2 Gui MG-KH" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,44 +21,23 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
-  <si>
-    <t xml:space="preserve">CÔNG TY CỔ PHẦN CHỨNG KHOÁN UP — BM-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DANH MỤC CHỨNG KHOÁN KÝ QUỸ (đính kèm Quyết định số ......../QĐ-TGĐ)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
+  <si>
+    <t xml:space="preserve">BM-02.1 · DANH MỤC KÝ QUỸ ĐẦY ĐỦ (nội bộ &amp; P.DVCK)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MV-08 · Mã · LTV · giá chặn · room · hạn mức. Ô nền vàng = nhập tay; Hạn mức tự tính.</t>
   </si>
   <si>
     <t xml:space="preserve">Kỳ áp dụng:</t>
   </si>
   <si>
-    <t xml:space="preserve">Tháng ...... / ........</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ngày hiệu lực:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">...... / ...... / ..........</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Người lập (NCPT):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">............................</t>
+    <t xml:space="preserve">Tháng …… / ………</t>
   </si>
   <si>
     <t xml:space="preserve">Mã CK</t>
   </si>
   <si>
-    <t xml:space="preserve">Sàn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhóm ngành</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phân loại</t>
-  </si>
-  <si>
     <t xml:space="preserve">LTV (%)</t>
   </si>
   <si>
@@ -67,57 +47,40 @@
     <t xml:space="preserve">Room (CP)</t>
   </si>
   <si>
-    <t xml:space="preserve">Hạn mức cho vay (đồng)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ngày hiệu lực</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ghi chú</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VNM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phi tài chính</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiêu chuẩn</t>
+    <t xml:space="preserve">Hạn mức (đồng)</t>
   </si>
   <si>
     <t xml:space="preserve">VCB</t>
   </si>
   <si>
-    <t xml:space="preserve">Tài chính</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XYZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cần theo dõi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TỔNG HẠN MỨC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ghi chú: Hạn mức cho vay = Room (CP) × Giá chặn. Phân loại: Tiêu chuẩn / Cần theo dõi / Không cho vay.</t>
+    <t xml:space="preserve">ACB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ℹ Hạn mức = Room × Giá chặn (tự tính). Danh sách mã · LTV · giá chặn · room theo kết quả Model (PL-01).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BM-02.2 · DANH MỤC GỬI MÔI GIỚI / KHÁCH HÀNG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MV-08 · Bản rút gọn: Mã · LTV · cờ giá chặn (0/1). Không public giá chặn, không gồm room/pool.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Giá chặn (0/1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ℹ 0 = không có giá chặn; 1 = có giá chặn. Bản này gửi MG/KH, KHÔNG bao gồm room/pool.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="#,##0"/>
+    <numFmt numFmtId="165" formatCode="0%"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,16 +105,16 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="13"/>
-      <color rgb="FF1F3864"/>
+      <sz val="14"/>
+      <color rgb="FF1E3A5F"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF2E5496"/>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF6B7280"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -159,6 +122,7 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
+      <color rgb="FF1E3A5F"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -171,31 +135,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="9"/>
-      <color rgb="FF808080"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -210,13 +150,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2E5496"/>
-        <bgColor rgb="FF1F3864"/>
+        <fgColor rgb="FFFFF7D6"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
+        <fgColor rgb="FFD5E8F0"/>
         <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
@@ -231,16 +171,16 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFB8C4D0"/>
       </left>
       <right style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFB8C4D0"/>
       </right>
       <top style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFB8C4D0"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFB8C4D0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -270,7 +210,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -287,47 +227,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -356,16 +280,16 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFBFBFBF"/>
+      <rgbColor rgb="FFB8C4D0"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFFF7D6"/>
+      <rgbColor rgb="FFD5E8F0"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD9E1F2"/>
+      <rgbColor rgb="FFCCCCFF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -388,15 +312,15 @@
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF6B7280"/>
       <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF1F3864"/>
+      <rgbColor rgb="FF1E3A5F"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF2E5496"/>
+      <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
     </indexedColors>
   </colors>
@@ -411,34 +335,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -583,22 +507,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -612,225 +531,138 @@
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
     </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>90000</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <f aca="false">C6*D6</f>
+        <v>18000000000</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <f aca="false">C7*D7</f>
+        <v>7500000000</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>5</v>
       </c>
+      <c r="C4" s="5" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="B5" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="B6" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>70000</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <f aca="false">F8*G8</f>
-        <v>175000000000</v>
-      </c>
-      <c r="I8" s="6"/>
-      <c r="J8" s="9"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>90000</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>13750000</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <f aca="false">F9*G9</f>
-        <v>1237500000000</v>
-      </c>
-      <c r="I9" s="6"/>
-      <c r="J9" s="9"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>15600</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>90000</v>
-      </c>
-      <c r="H10" s="8" t="n">
-        <f aca="false">F10*G10</f>
-        <v>1404000000</v>
-      </c>
-      <c r="I10" s="6"/>
-      <c r="J10" s="9"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="11" t="str">
-        <f aca="false">IF(AND(F11&lt;&gt;"",G11&lt;&gt;""),F11*G11,"")</f>
-        <v/>
-      </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="11" t="str">
-        <f aca="false">IF(AND(F12&lt;&gt;"",G12&lt;&gt;""),F12*G12,"")</f>
-        <v/>
-      </c>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="11" t="str">
-        <f aca="false">IF(AND(F13&lt;&gt;"",G13&lt;&gt;""),F13*G13,"")</f>
-        <v/>
-      </c>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="11" t="str">
-        <f aca="false">IF(AND(F14&lt;&gt;"",G14&lt;&gt;""),F14*G14,"")</f>
-        <v/>
-      </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="13" t="n">
-        <f aca="false">SUM(H8:H14)</f>
-        <v>1413904000000</v>
-      </c>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
